--- a/sample_data/SVP.xlsx
+++ b/sample_data/SVP.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>252106</v>
+        <v>76680</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>175695</v>
+        <v>64003</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>237908</v>
+        <v>76386</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>194852</v>
+        <v>63537</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>246531</v>
+        <v>73048</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>187961</v>
+        <v>67629</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>272619</v>
+        <v>70982</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>180166</v>
+        <v>68087</v>
       </c>
     </row>
     <row r="10">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>230655</v>
+        <v>74204</v>
       </c>
     </row>
     <row r="11">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>183063</v>
+        <v>70574</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>259873</v>
+        <v>66334</v>
       </c>
     </row>
     <row r="13">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>181766</v>
+        <v>69201</v>
       </c>
     </row>
     <row r="14">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>228334</v>
+        <v>72730</v>
       </c>
     </row>
     <row r="15">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>179802</v>
+        <v>68657</v>
       </c>
     </row>
     <row r="16">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>263199</v>
+        <v>69225</v>
       </c>
     </row>
     <row r="17">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>169471</v>
+        <v>65167</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>253773</v>
+        <v>69726</v>
       </c>
     </row>
     <row r="19">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>184571</v>
+        <v>72020</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>252009</v>
+        <v>70649</v>
       </c>
     </row>
     <row r="21">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>190699</v>
+        <v>62818</v>
       </c>
     </row>
     <row r="22">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>267225</v>
+        <v>77688</v>
       </c>
     </row>
     <row r="23">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>167314</v>
+        <v>70411</v>
       </c>
     </row>
     <row r="24">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>242990</v>
+        <v>75919</v>
       </c>
     </row>
     <row r="25">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>187415</v>
+        <v>67789</v>
       </c>
     </row>
     <row r="26">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>250356</v>
+        <v>67182</v>
       </c>
     </row>
     <row r="27">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>195578</v>
+        <v>67069</v>
       </c>
     </row>
     <row r="28">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>274537</v>
+        <v>72558</v>
       </c>
     </row>
     <row r="29">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>174950</v>
+        <v>67385</v>
       </c>
     </row>
     <row r="30">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>255971</v>
+        <v>69977</v>
       </c>
     </row>
     <row r="31">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>180034</v>
+        <v>65945</v>
       </c>
     </row>
   </sheetData>
